--- a/tables/Opioid_Tier2_Qualitative.xlsx
+++ b/tables/Opioid_Tier2_Qualitative.xlsx
@@ -492,13 +492,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Group means (Tx vs Ctrl)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>22.5 vs 13.9</t>
-        </is>
+          <t>Exposure-response linear mixed-effects regression slope (change from baseline, placebo-corrected QTcI vs. plasma noribogaine concentration)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.17</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -517,7 +515,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Time to OST resumption 22.5 h vs 13.9 h (noribogaine 120mg vs placebo); difference non-significant.</t>
+          <t>The article's only SUD-relevant outcome -- opioid withdrawal ratings (SOWS/OOWS/COWS) and time to resumption of OST -- showed a nonstatistically significant trend toward reduced withdrawal at 120 mg, and near-identical placebo-vs-active time-to-OST-resumption within cohorts (Pearson r=0.993), which the authors attribute to a design confound (shared housing/observation making OST resumption obvious to co-housed participants) rather than to a genuine null effect. No SUD outcome reached significance in either direction.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -546,7 +544,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25 vs 3</t>
+          <t>50 vs 60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -556,102 +554,98 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>moderate_positive</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Computed OR≈10.78 from approximate two-group abstinence proportions (25% vs 3% at 12mo, read from Fig. 1); sustained across 24mo.</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>10.78</v>
-      </c>
+          <t>High-dose (psychedelic) ketamine group showed significantly higher abstinence / lower relapse than the low-dose active-placebo group from month 1 through nearly all of the 24-month follow-up (Section 3.2), plus greater and longer-lasting craving reduction (Section 3.3) and greater positive change on the Color Test of Attitudes (Section 3.11) — a directionally clear, sustained advantage for the higher psychedelic dose, though without a precise pooled effect size.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Krupitsky 2007</t>
+          <t>P.L. Prior 2014</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>Ibogaine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50 vs 22.2</t>
-        </is>
+          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.45</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
+          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>moderate_positive</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>3.5</v>
-      </c>
+          <t>Two-arm double-blind placebo-controlled pilot RCT; ibogaine group showed a significantly lower positive-urine (relapse) rate than placebo across 24-week follow-up (F(3,12)=2.45, p=0.023), corroborated by a large, significant reduction in MCCS craving scores in the ibogaine arm vs no change in placebo (p&lt;0.0001). Graded moderate rather than large because the primary urine-positivity effect itself is not reported in a directly quantifiable, group-comparable form (no paired percentages); graded above small/null given significance and consistent direction across two independent outcome measures.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P.L. Prior 2014</t>
+          <t>Krupitsky 2007</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.45</v>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50 vs 22.2</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
+          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -666,10 +660,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Double-blind placebo-controlled pilot; ibogaine group had 10% positive urine at follow-up; F(3,12)=2.450, p=0.023 per source.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,9 +676,7 @@
       <c r="B6" t="n">
         <v>2000</v>
       </c>
-      <c r="C6" t="n">
-        <v>27</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Ibogaine</t>
@@ -690,11 +684,13 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>9.59</v>
+          <t>F (multi-df, within-subjects repeated-measures ANOVA)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>F(3,24) = 81.38</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -713,7 +709,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BDI improved from 16.86 to 2.29 (F(3,18)=9.59, p&lt;0.001); single-arm ibogaine study with no comparator group.</t>
+          <t>Single-arm open-label ibogaine trial with no control group. All 5 HCQN-29 opiate-craving subscales (TABLE 2, all p&lt;=.0001) and 3 of 5 CCQN-45 cocaine-craving subscales (TABLE 3) showed statistically significant pre-to-post reductions, and BDI depression scores also decreased significantly across the study (F(3,18)=9.59, p=.0005, TABLE 1) -- a consistently positive pre/post direction across every reported outcome family, with no comparator arm to benchmark against.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/tables/Opioid_Tier2_Qualitative.xlsx
+++ b/tables/Opioid_Tier2_Qualitative.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,31 +572,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P.L. Prior 2014</t>
+          <t>Jovaisa T 2006</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
+          <t>Cohen's d</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
+          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. output.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Two-arm double-blind placebo-controlled pilot RCT; ibogaine group showed a significantly lower positive-urine (relapse) rate than placebo across 24-week follow-up (F(3,12)=2.45, p=0.023), corroborated by a large, significant reduction in MCCS craving scores in the ibogaine arm vs no change in placebo (p&lt;0.0001). Graded moderate rather than large because the primary urine-positivity effect itself is not reported in a directly quantifiable, group-comparable form (no paired percentages); graded above small/null given significance and consistent direction across two independent outcome measures.</t>
+          <t>Randomised, blinded two-group trial of ketamine as an adjuvant to opioid-antagonist induction. The ketamine arm showed significantly less severe withdrawal on the hourly OOWS-A score (p&lt;0.05) and the authors conclude the ketamine group "presented better control of withdrawal symptoms" — a directionally clear, statistically significant between-group advantage on the primary SUD outcome, but reported without a test statistic or group means, so no effect size is derivable. Graded moderate rather than large on the strength of a single significant withdrawal-severity comparison.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -619,100 +619,149 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Krupitsky 2007</t>
+          <t>P.L. Prior 2014</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>Ibogaine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50 vs 22.2</t>
-        </is>
+          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.45</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
+          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>moderate_positive</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3.5</v>
-      </c>
+          <t>Two-arm double-blind placebo-controlled pilot RCT; ibogaine group showed a significantly lower positive-urine (relapse) rate than placebo across 24-week follow-up (F(3,12)=2.45, p=0.023), corroborated by a large, significant reduction in MCCS craving scores in the ibogaine arm vs no change in placebo (p&lt;0.0001). Graded moderate rather than large because the primary urine-positivity effect itself is not reported in a directly quantifiable, group-comparable form (no paired percentages); graded above small/null given significance and consistent direction across two independent outcome measures.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Krupitsky 2007</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C6" t="n">
+        <v>53</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ketamine</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50 vs 22.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>large_positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>D.C. Mash 2000</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>2000</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Ibogaine</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>F (multi-df, within-subjects repeated-measures ANOVA)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>F(3,24) = 81.38</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>F(3,18) multi-df; within-group pre-post design; no comparator arm</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>single_arm_positive</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Positive (Single-arm, no comparator)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Single-arm open-label ibogaine trial with no control group. All 5 HCQN-29 opiate-craving subscales (TABLE 2, all p&lt;=.0001) and 3 of 5 CCQN-45 cocaine-craving subscales (TABLE 3) showed statistically significant pre-to-post reductions, and BDI depression scores also decreased significantly across the study (F(3,18)=9.59, p=.0005, TABLE 1) -- a consistently positive pre/post direction across every reported outcome family, with no comparator arm to benchmark against.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Opioid_Tier2_Qualitative.xlsx
+++ b/tables/Opioid_Tier2_Qualitative.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,149 +619,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P.L. Prior 2014</t>
+          <t>Krupitsky 2007</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.45</v>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50 vs 22.2</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>F(3,12) has 3-df numerator; not reducible to 1-df between-groups comparison</t>
+          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>moderate_positive</t>
+          <t>large_positive</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Moderate Positive (OR 1.5-3 or g 0.5-0.8)</t>
+          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Two-arm double-blind placebo-controlled pilot RCT; ibogaine group showed a significantly lower positive-urine (relapse) rate than placebo across 24-week follow-up (F(3,12)=2.45, p=0.023), corroborated by a large, significant reduction in MCCS craving scores in the ibogaine arm vs no change in placebo (p&lt;0.0001). Graded moderate rather than large because the primary urine-positivity effect itself is not reported in a directly quantifiable, group-comparable form (no paired percentages); graded above small/null given significance and consistent direction across two independent outcome measures.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Krupitsky 2007</t>
+          <t>D.C. Mash 2000</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>Ibogaine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
+          <t>F (multi-df, within-subjects repeated-measures ANOVA)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50 vs 22.2</t>
+          <t>F(3,24) = 81.38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Two-group proportions; no SD reported; downgrade to Tier 2</t>
+          <t>F(3,18) multi-df; within-group pre-post design; no comparator arm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>large_positive</t>
+          <t>single_arm_positive</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Large Positive (OR&gt;=3 or g&gt;=0.8)</t>
+          <t>Positive (Single-arm, no comparator)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Computed OR=3.50 from two-group abstinence proportions (50% vs 22.2% at 12mo); exceeds OR≥3 threshold.</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>D.C. Mash 2000</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ibogaine</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>F (multi-df, within-subjects repeated-measures ANOVA)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>F(3,24) = 81.38</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>F(3,18) multi-df; within-group pre-post design; no comparator arm</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>single_arm_positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Positive (Single-arm, no comparator)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>Single-arm open-label ibogaine trial with no control group. All 5 HCQN-29 opiate-craving subscales (TABLE 2, all p&lt;=.0001) and 3 of 5 CCQN-45 cocaine-craving subscales (TABLE 3) showed statistically significant pre-to-post reductions, and BDI depression scores also decreased significantly across the study (F(3,18)=9.59, p=.0005, TABLE 1) -- a consistently positive pre/post direction across every reported outcome family, with no comparator arm to benchmark against.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Opioid_Tier2_Qualitative.xlsx
+++ b/tables/Opioid_Tier2_Qualitative.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. output.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
+          <t>Excluded from Tier 1: the only convertible statistic (d=1.39 from peak MAP, 96.6 vs 79.4 mmHg) measures blood pressure, not substance use. clinical_adjudication.md rules the OOWS-A withdrawal-severity score the primary outcome, and it is reported only as 'p&lt;0.05' with no test statistic, so no SUD-outcome effect size can be derived without computing a test the authors did not report.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
